--- a/examples/excel/charts-histogram.xlsx
+++ b/examples/excel/charts-histogram.xlsx
@@ -3,10 +3,10 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Binning Modes" sheetId="1" r:id="rId1"/>
-    <x:sheet name="2-Styled Histograms" sheetId="2" r:id="Reca47830830846ba"/>
-    <x:sheet name="3-Typography &amp; Colors" sheetId="3" r:id="R89c35bff95754f0a"/>
-    <x:sheet name="4-Distribution Gallery" sheetId="4" r:id="R331eb3c01b7f4f85"/>
-    <x:sheet name="5-Parity Knobs" sheetId="5" r:id="R82bce404d8ec4c71"/>
+    <x:sheet name="2-Styled Histograms" sheetId="2" r:id="Rba3756bed874480c"/>
+    <x:sheet name="3-Typography &amp; Colors" sheetId="3" r:id="R0d9edd247b5e4e17"/>
+    <x:sheet name="4-Distribution Gallery" sheetId="4" r:id="R4b9d43af1ab5472e"/>
+    <x:sheet name="5-Parity Knobs" sheetId="5" r:id="R899274bce0c84082"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -37,7 +37,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R9361ae5e7238472b"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re7f0d05ec8494a97"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -67,7 +67,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0f9c65c8261e4f73"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R809c1f1e96cc4f32"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -97,7 +97,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re423e1f3418e4cce"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R16762ef8734a45a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -127,7 +127,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R65aa6c39c74e44c0"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0d4e70d9d4a34419"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -162,7 +162,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4ca1049b4476462b"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rcd39a22b89194307"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -192,7 +192,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R81d7c183fa0f4f16"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1f39b5ff4bf34320"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -222,7 +222,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R36a925e1abd44e6e"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R7338b42a152a4128"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -252,7 +252,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rda2f95545e064323"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R71eb8ff02a614278"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -287,7 +287,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf5bedcff12374fee"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rc7ced2618124492d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -317,7 +317,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4d013f53447549d4"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R2e5fc42a5f5d439d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -347,7 +347,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R7439f86712724e1b"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re9884edb80b94008"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -377,7 +377,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R02790aa80baf4338"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R214d9eef97d348b3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -412,7 +412,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R063dbe22405e47ac"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R79bf49b612154c8d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -442,7 +442,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R70b76a74773141fb"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rbc402190b76a4e42"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -472,7 +472,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R8b751fce936048eb"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R25ba3445286f4c55"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -502,7 +502,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R849dfed31b444f8a"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R681af248723a4744"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -532,7 +532,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R88118cec4db541fe"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R174630eb7dce421a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -562,7 +562,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R235d1c49159c44c5"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rddba70ae2fed4383"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -597,7 +597,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R45df076f6b3248c4"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rd41eab45a0af40f7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -627,7 +627,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R06b004a8ae964fd9"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R206310bf125a4cff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -657,7 +657,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rea6c9cc615d042f1"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R5e6c93fd0f684e86"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -687,7 +687,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra3089544a7c841bc"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R41b2cd04bb114719"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -717,7 +717,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra7449cae6a3a47d9"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0ae4ed63f3d14e6a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -747,7 +747,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf35b0b241e90448c"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re478fbc9254b400e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6404,18 +6404,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -6926,18 +6914,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -7448,18 +7424,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -7970,18 +7934,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -8492,18 +8444,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -9014,18 +8954,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -9536,18 +9464,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -10058,18 +9974,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -10580,18 +10484,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -11102,18 +10994,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -11624,18 +11504,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -12146,18 +12014,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -12668,18 +12524,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -13190,18 +13034,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -13712,18 +13544,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -14234,18 +14054,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -14756,18 +14564,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -15278,18 +15074,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -15800,18 +15584,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -16322,18 +16094,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -16844,18 +16604,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -17366,18 +17114,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -17888,18 +17624,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -18410,18 +18134,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
@@ -18923,34 +18635,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669b1ccf5dda4025"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R164b09332d5e4f4c"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a0baaf4fd94d7a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R410f7074361d4b8f"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0eabc7bae204d10"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6733d1fd37144807"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bb9ee5c6f87476e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2531b3d721ab4cc5"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f6ff80fe8fa403e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3743c0eaab343bc"/>
 </x:worksheet>
 </file>